--- a/Xlsx/Activity/Activity.xlsx
+++ b/Xlsx/Activity/Activity.xlsx
@@ -1187,6 +1187,12 @@
       <c r="E4" t="s">
         <v>21</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Xlsx/Activity/Activity.xlsx
+++ b/Xlsx/Activity/Activity.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27360" windowHeight="13260"/>
+    <workbookView windowWidth="21090" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="property" sheetId="1" r:id="rId1"/>
@@ -56,10 +56,10 @@
     <t>SortWeight</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
+    <t>String</t>
+  </si>
+  <si>
+    <t>Int</t>
   </si>
   <si>
     <t>活动类型</t>
